--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1610,6 +1610,1290 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122291605</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>403645</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7063935</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122291606</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>403596</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7063889</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122291608</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>403527</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7063901</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122291612</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78643</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>403831</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7063783</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122291604</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>403688</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7064029</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122291603</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>403760</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7064050</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122291609</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>403530</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7063892</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122291607</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>403575</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7063889</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122291615</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78643</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>403553</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7063909</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122291601</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>403785</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7064065</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122291602</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>403779</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7064045</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122291610</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>403537</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7063905</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291605</v>
+        <v>122291601</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403645</v>
+        <v>403785</v>
       </c>
       <c r="R10" t="n">
-        <v>7063935</v>
+        <v>7064065</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291606</v>
+        <v>122291605</v>
       </c>
       <c r="B11" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403596</v>
+        <v>403645</v>
       </c>
       <c r="R11" t="n">
-        <v>7063889</v>
+        <v>7063935</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291608</v>
+        <v>122291602</v>
       </c>
       <c r="B12" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403527</v>
+        <v>403779</v>
       </c>
       <c r="R12" t="n">
-        <v>7063901</v>
+        <v>7064045</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291612</v>
+        <v>122291607</v>
       </c>
       <c r="B13" t="n">
-        <v>78643</v>
+        <v>57374</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403831</v>
+        <v>403575</v>
       </c>
       <c r="R13" t="n">
-        <v>7063783</v>
+        <v>7063889</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291604</v>
+        <v>122291608</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403688</v>
+        <v>403527</v>
       </c>
       <c r="R14" t="n">
-        <v>7064029</v>
+        <v>7063901</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291603</v>
+        <v>122291606</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403760</v>
+        <v>403596</v>
       </c>
       <c r="R15" t="n">
-        <v>7064050</v>
+        <v>7063889</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291609</v>
+        <v>122291615</v>
       </c>
       <c r="B16" t="n">
-        <v>57372</v>
+        <v>78645</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403530</v>
+        <v>403553</v>
       </c>
       <c r="R16" t="n">
-        <v>7063892</v>
+        <v>7063909</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291607</v>
+        <v>122291610</v>
       </c>
       <c r="B17" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403575</v>
+        <v>403537</v>
       </c>
       <c r="R17" t="n">
-        <v>7063889</v>
+        <v>7063905</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291615</v>
+        <v>122291603</v>
       </c>
       <c r="B18" t="n">
-        <v>78643</v>
+        <v>57374</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403553</v>
+        <v>403760</v>
       </c>
       <c r="R18" t="n">
-        <v>7063909</v>
+        <v>7064050</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291601</v>
+        <v>122291609</v>
       </c>
       <c r="B19" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403785</v>
+        <v>403530</v>
       </c>
       <c r="R19" t="n">
-        <v>7064065</v>
+        <v>7063892</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291602</v>
+        <v>122291612</v>
       </c>
       <c r="B20" t="n">
-        <v>57372</v>
+        <v>78645</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403779</v>
+        <v>403831</v>
       </c>
       <c r="R20" t="n">
-        <v>7064045</v>
+        <v>7063783</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291610</v>
+        <v>122291604</v>
       </c>
       <c r="B21" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403537</v>
+        <v>403688</v>
       </c>
       <c r="R21" t="n">
-        <v>7063905</v>
+        <v>7064029</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,7 +1613,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291601</v>
+        <v>122291609</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403785</v>
+        <v>403530</v>
       </c>
       <c r="R10" t="n">
-        <v>7064065</v>
+        <v>7063892</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291605</v>
+        <v>122291603</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403645</v>
+        <v>403760</v>
       </c>
       <c r="R11" t="n">
-        <v>7063935</v>
+        <v>7064050</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291602</v>
+        <v>122291612</v>
       </c>
       <c r="B12" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403779</v>
+        <v>403831</v>
       </c>
       <c r="R12" t="n">
-        <v>7064045</v>
+        <v>7063783</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291607</v>
+        <v>122291604</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403575</v>
+        <v>403688</v>
       </c>
       <c r="R13" t="n">
-        <v>7063889</v>
+        <v>7064029</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291608</v>
+        <v>122291606</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403527</v>
+        <v>403596</v>
       </c>
       <c r="R14" t="n">
-        <v>7063901</v>
+        <v>7063889</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,10 +2148,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291606</v>
+        <v>122291615</v>
       </c>
       <c r="B15" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2164,21 +2164,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403596</v>
+        <v>403553</v>
       </c>
       <c r="R15" t="n">
-        <v>7063889</v>
+        <v>7063909</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291615</v>
+        <v>122291608</v>
       </c>
       <c r="B16" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403553</v>
+        <v>403527</v>
       </c>
       <c r="R16" t="n">
-        <v>7063909</v>
+        <v>7063901</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291610</v>
+        <v>122291605</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403537</v>
+        <v>403645</v>
       </c>
       <c r="R17" t="n">
-        <v>7063905</v>
+        <v>7063935</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,7 +2469,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291603</v>
+        <v>122291607</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403760</v>
+        <v>403575</v>
       </c>
       <c r="R18" t="n">
-        <v>7064050</v>
+        <v>7063889</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291609</v>
+        <v>122291602</v>
       </c>
       <c r="B19" t="n">
         <v>57374</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403530</v>
+        <v>403779</v>
       </c>
       <c r="R19" t="n">
-        <v>7063892</v>
+        <v>7064045</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291612</v>
+        <v>122291601</v>
       </c>
       <c r="B20" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403831</v>
+        <v>403785</v>
       </c>
       <c r="R20" t="n">
-        <v>7063783</v>
+        <v>7064065</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,7 +2790,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291604</v>
+        <v>122291610</v>
       </c>
       <c r="B21" t="n">
         <v>57374</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403688</v>
+        <v>403537</v>
       </c>
       <c r="R21" t="n">
-        <v>7064029</v>
+        <v>7063905</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,7 +1613,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291601</v>
+        <v>122291608</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403785</v>
+        <v>403527</v>
       </c>
       <c r="R10" t="n">
-        <v>7064065</v>
+        <v>7063901</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,7 +1720,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291610</v>
+        <v>122291607</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403537</v>
+        <v>403575</v>
       </c>
       <c r="R11" t="n">
-        <v>7063905</v>
+        <v>7063889</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291607</v>
+        <v>122291610</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403575</v>
+        <v>403537</v>
       </c>
       <c r="R12" t="n">
-        <v>7063889</v>
+        <v>7063905</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291612</v>
+        <v>122291601</v>
       </c>
       <c r="B13" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403831</v>
+        <v>403785</v>
       </c>
       <c r="R13" t="n">
-        <v>7063783</v>
+        <v>7064065</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291609</v>
+        <v>122291615</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403530</v>
+        <v>403553</v>
       </c>
       <c r="R14" t="n">
-        <v>7063892</v>
+        <v>7063909</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2148,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291604</v>
+        <v>122291606</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403688</v>
+        <v>403596</v>
       </c>
       <c r="R15" t="n">
-        <v>7064029</v>
+        <v>7063889</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291603</v>
+        <v>122291612</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403760</v>
+        <v>403831</v>
       </c>
       <c r="R16" t="n">
-        <v>7064050</v>
+        <v>7063783</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291615</v>
+        <v>122291609</v>
       </c>
       <c r="B17" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2378,21 +2378,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403553</v>
+        <v>403530</v>
       </c>
       <c r="R17" t="n">
-        <v>7063909</v>
+        <v>7063892</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,7 +2469,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291605</v>
+        <v>122291604</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403645</v>
+        <v>403688</v>
       </c>
       <c r="R18" t="n">
-        <v>7063935</v>
+        <v>7064029</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291602</v>
+        <v>122291605</v>
       </c>
       <c r="B19" t="n">
         <v>57374</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403779</v>
+        <v>403645</v>
       </c>
       <c r="R19" t="n">
-        <v>7064045</v>
+        <v>7063935</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,7 +2683,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291606</v>
+        <v>122291602</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403596</v>
+        <v>403779</v>
       </c>
       <c r="R20" t="n">
-        <v>7063889</v>
+        <v>7064045</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291608</v>
+        <v>122291603</v>
       </c>
       <c r="B21" t="n">
         <v>57374</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403527</v>
+        <v>403760</v>
       </c>
       <c r="R21" t="n">
-        <v>7063901</v>
+        <v>7064050</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,7 +1613,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291608</v>
+        <v>122291605</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403527</v>
+        <v>403645</v>
       </c>
       <c r="R10" t="n">
-        <v>7063901</v>
+        <v>7063935</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291607</v>
+        <v>122291612</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403575</v>
+        <v>403831</v>
       </c>
       <c r="R11" t="n">
-        <v>7063889</v>
+        <v>7063783</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291610</v>
+        <v>122291609</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403537</v>
+        <v>403530</v>
       </c>
       <c r="R12" t="n">
-        <v>7063905</v>
+        <v>7063892</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291601</v>
+        <v>122291604</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403785</v>
+        <v>403688</v>
       </c>
       <c r="R13" t="n">
-        <v>7064065</v>
+        <v>7064029</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291615</v>
+        <v>122291602</v>
       </c>
       <c r="B14" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403553</v>
+        <v>403779</v>
       </c>
       <c r="R14" t="n">
-        <v>7063909</v>
+        <v>7064045</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2148,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291606</v>
+        <v>122291607</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403596</v>
+        <v>403575</v>
       </c>
       <c r="R15" t="n">
         <v>7063889</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291612</v>
+        <v>122291606</v>
       </c>
       <c r="B16" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403831</v>
+        <v>403596</v>
       </c>
       <c r="R16" t="n">
-        <v>7063783</v>
+        <v>7063889</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291609</v>
+        <v>122291608</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403530</v>
+        <v>403527</v>
       </c>
       <c r="R17" t="n">
-        <v>7063892</v>
+        <v>7063901</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,7 +2469,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291604</v>
+        <v>122291601</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403688</v>
+        <v>403785</v>
       </c>
       <c r="R18" t="n">
-        <v>7064029</v>
+        <v>7064065</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291605</v>
+        <v>122291603</v>
       </c>
       <c r="B19" t="n">
         <v>57374</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403645</v>
+        <v>403760</v>
       </c>
       <c r="R19" t="n">
-        <v>7063935</v>
+        <v>7064050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291602</v>
+        <v>122291610</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403779</v>
+        <v>403537</v>
       </c>
       <c r="R20" t="n">
-        <v>7064045</v>
+        <v>7063905</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291603</v>
+        <v>122291615</v>
       </c>
       <c r="B21" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403760</v>
+        <v>403553</v>
       </c>
       <c r="R21" t="n">
-        <v>7064050</v>
+        <v>7063909</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,7 +1613,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291605</v>
+        <v>122291607</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403645</v>
+        <v>403575</v>
       </c>
       <c r="R10" t="n">
-        <v>7063935</v>
+        <v>7063889</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291612</v>
+        <v>122291609</v>
       </c>
       <c r="B11" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403831</v>
+        <v>403530</v>
       </c>
       <c r="R11" t="n">
-        <v>7063783</v>
+        <v>7063892</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291609</v>
+        <v>122291615</v>
       </c>
       <c r="B12" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403530</v>
+        <v>403553</v>
       </c>
       <c r="R12" t="n">
-        <v>7063892</v>
+        <v>7063909</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291604</v>
+        <v>122291605</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403688</v>
+        <v>403645</v>
       </c>
       <c r="R13" t="n">
-        <v>7064029</v>
+        <v>7063935</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291602</v>
+        <v>122291608</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403779</v>
+        <v>403527</v>
       </c>
       <c r="R14" t="n">
-        <v>7064045</v>
+        <v>7063901</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2148,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291607</v>
+        <v>122291601</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403575</v>
+        <v>403785</v>
       </c>
       <c r="R15" t="n">
-        <v>7063889</v>
+        <v>7064065</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2255,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291606</v>
+        <v>122291604</v>
       </c>
       <c r="B16" t="n">
         <v>57374</v>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403596</v>
+        <v>403688</v>
       </c>
       <c r="R16" t="n">
-        <v>7063889</v>
+        <v>7064029</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291608</v>
+        <v>122291603</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403527</v>
+        <v>403760</v>
       </c>
       <c r="R17" t="n">
-        <v>7063901</v>
+        <v>7064050</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291601</v>
+        <v>122291606</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403785</v>
+        <v>403596</v>
       </c>
       <c r="R18" t="n">
-        <v>7064065</v>
+        <v>7063889</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291603</v>
+        <v>122291610</v>
       </c>
       <c r="B19" t="n">
         <v>57374</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403760</v>
+        <v>403537</v>
       </c>
       <c r="R19" t="n">
-        <v>7064050</v>
+        <v>7063905</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,7 +2683,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291610</v>
+        <v>122291602</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403537</v>
+        <v>403779</v>
       </c>
       <c r="R20" t="n">
-        <v>7063905</v>
+        <v>7064045</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291615</v>
+        <v>122291612</v>
       </c>
       <c r="B21" t="n">
         <v>78646</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403553</v>
+        <v>403831</v>
       </c>
       <c r="R21" t="n">
-        <v>7063909</v>
+        <v>7063783</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291610</v>
+        <v>122291612</v>
       </c>
       <c r="B19" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403537</v>
+        <v>403831</v>
       </c>
       <c r="R19" t="n">
-        <v>7063905</v>
+        <v>7063783</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,7 +2683,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291602</v>
+        <v>122291610</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403779</v>
+        <v>403537</v>
       </c>
       <c r="R20" t="n">
-        <v>7064045</v>
+        <v>7063905</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291612</v>
+        <v>122291602</v>
       </c>
       <c r="B21" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403831</v>
+        <v>403779</v>
       </c>
       <c r="R21" t="n">
-        <v>7063783</v>
+        <v>7064045</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291607</v>
+        <v>122291608</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403575</v>
+        <v>403527</v>
       </c>
       <c r="R10" t="n">
-        <v>7063889</v>
+        <v>7063901</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291609</v>
+        <v>122291612</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403530</v>
+        <v>403831</v>
       </c>
       <c r="R11" t="n">
-        <v>7063892</v>
+        <v>7063783</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,7 +1830,7 @@
         <v>122291615</v>
       </c>
       <c r="B12" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291605</v>
+        <v>122291601</v>
       </c>
       <c r="B13" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403645</v>
+        <v>403785</v>
       </c>
       <c r="R13" t="n">
-        <v>7063935</v>
+        <v>7064065</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291608</v>
+        <v>122291603</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403527</v>
+        <v>403760</v>
       </c>
       <c r="R14" t="n">
-        <v>7063901</v>
+        <v>7064050</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291601</v>
+        <v>122291605</v>
       </c>
       <c r="B15" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403785</v>
+        <v>403645</v>
       </c>
       <c r="R15" t="n">
-        <v>7064065</v>
+        <v>7063935</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291604</v>
+        <v>122291602</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403688</v>
+        <v>403779</v>
       </c>
       <c r="R16" t="n">
-        <v>7064029</v>
+        <v>7064045</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291603</v>
+        <v>122291607</v>
       </c>
       <c r="B17" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403760</v>
+        <v>403575</v>
       </c>
       <c r="R17" t="n">
-        <v>7064050</v>
+        <v>7063889</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291606</v>
+        <v>122291609</v>
       </c>
       <c r="B18" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403596</v>
+        <v>403530</v>
       </c>
       <c r="R18" t="n">
-        <v>7063889</v>
+        <v>7063892</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291612</v>
+        <v>122291606</v>
       </c>
       <c r="B19" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403831</v>
+        <v>403596</v>
       </c>
       <c r="R19" t="n">
-        <v>7063783</v>
+        <v>7063889</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291610</v>
+        <v>122291604</v>
       </c>
       <c r="B20" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403537</v>
+        <v>403688</v>
       </c>
       <c r="R20" t="n">
-        <v>7063905</v>
+        <v>7064029</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291602</v>
+        <v>122291610</v>
       </c>
       <c r="B21" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403779</v>
+        <v>403537</v>
       </c>
       <c r="R21" t="n">
-        <v>7064045</v>
+        <v>7063905</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,7 +1613,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291608</v>
+        <v>122291603</v>
       </c>
       <c r="B10" t="n">
         <v>57379</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403527</v>
+        <v>403760</v>
       </c>
       <c r="R10" t="n">
-        <v>7063901</v>
+        <v>7064050</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291612</v>
+        <v>122291602</v>
       </c>
       <c r="B11" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403831</v>
+        <v>403779</v>
       </c>
       <c r="R11" t="n">
-        <v>7063783</v>
+        <v>7064045</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291615</v>
+        <v>122291608</v>
       </c>
       <c r="B12" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403553</v>
+        <v>403527</v>
       </c>
       <c r="R12" t="n">
-        <v>7063909</v>
+        <v>7063901</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291601</v>
+        <v>122291606</v>
       </c>
       <c r="B13" t="n">
         <v>57379</v>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403785</v>
+        <v>403596</v>
       </c>
       <c r="R13" t="n">
-        <v>7064065</v>
+        <v>7063889</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291603</v>
+        <v>122291610</v>
       </c>
       <c r="B14" t="n">
         <v>57379</v>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403760</v>
+        <v>403537</v>
       </c>
       <c r="R14" t="n">
-        <v>7064050</v>
+        <v>7063905</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2148,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291605</v>
+        <v>122291609</v>
       </c>
       <c r="B15" t="n">
         <v>57379</v>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403645</v>
+        <v>403530</v>
       </c>
       <c r="R15" t="n">
-        <v>7063935</v>
+        <v>7063892</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2255,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291602</v>
+        <v>122291605</v>
       </c>
       <c r="B16" t="n">
         <v>57379</v>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403779</v>
+        <v>403645</v>
       </c>
       <c r="R16" t="n">
-        <v>7064045</v>
+        <v>7063935</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291607</v>
+        <v>122291601</v>
       </c>
       <c r="B17" t="n">
         <v>57379</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403575</v>
+        <v>403785</v>
       </c>
       <c r="R17" t="n">
-        <v>7063889</v>
+        <v>7064065</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291609</v>
+        <v>122291615</v>
       </c>
       <c r="B18" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403530</v>
+        <v>403553</v>
       </c>
       <c r="R18" t="n">
-        <v>7063892</v>
+        <v>7063909</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291606</v>
+        <v>122291607</v>
       </c>
       <c r="B19" t="n">
         <v>57379</v>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403596</v>
+        <v>403575</v>
       </c>
       <c r="R19" t="n">
         <v>7063889</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291604</v>
+        <v>122291612</v>
       </c>
       <c r="B20" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403688</v>
+        <v>403831</v>
       </c>
       <c r="R20" t="n">
-        <v>7064029</v>
+        <v>7063783</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,7 +2790,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291610</v>
+        <v>122291604</v>
       </c>
       <c r="B21" t="n">
         <v>57379</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403537</v>
+        <v>403688</v>
       </c>
       <c r="R21" t="n">
-        <v>7063905</v>
+        <v>7064029</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,7 +1613,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291603</v>
+        <v>122291601</v>
       </c>
       <c r="B10" t="n">
         <v>57379</v>
@@ -1631,11 +1631,6 @@
       <c r="E10" t="n">
         <v>100109</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403760</v>
+        <v>403785</v>
       </c>
       <c r="R10" t="n">
-        <v>7064050</v>
+        <v>7064065</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1688,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,7 +1715,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291602</v>
+        <v>122291603</v>
       </c>
       <c r="B11" t="n">
         <v>57379</v>
@@ -1738,11 +1733,6 @@
       <c r="E11" t="n">
         <v>100109</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1760,10 +1750,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403779</v>
+        <v>403760</v>
       </c>
       <c r="R11" t="n">
-        <v>7064045</v>
+        <v>7064050</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1790,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,7 +1817,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291608</v>
+        <v>122291602</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -1845,11 +1835,6 @@
       <c r="E12" t="n">
         <v>100109</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1867,10 +1852,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403527</v>
+        <v>403779</v>
       </c>
       <c r="R12" t="n">
-        <v>7063901</v>
+        <v>7064045</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1892,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,7 +1919,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291606</v>
+        <v>122291605</v>
       </c>
       <c r="B13" t="n">
         <v>57379</v>
@@ -1952,11 +1937,6 @@
       <c r="E13" t="n">
         <v>100109</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1974,10 +1954,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403596</v>
+        <v>403645</v>
       </c>
       <c r="R13" t="n">
-        <v>7063889</v>
+        <v>7063935</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +1994,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,7 +2021,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291610</v>
+        <v>122291606</v>
       </c>
       <c r="B14" t="n">
         <v>57379</v>
@@ -2059,11 +2039,6 @@
       <c r="E14" t="n">
         <v>100109</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2081,10 +2056,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403537</v>
+        <v>403596</v>
       </c>
       <c r="R14" t="n">
-        <v>7063905</v>
+        <v>7063889</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2166,11 +2141,6 @@
       <c r="E15" t="n">
         <v>100109</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2255,7 +2225,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291605</v>
+        <v>122291607</v>
       </c>
       <c r="B16" t="n">
         <v>57379</v>
@@ -2273,11 +2243,6 @@
       <c r="E16" t="n">
         <v>100109</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2295,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403645</v>
+        <v>403575</v>
       </c>
       <c r="R16" t="n">
-        <v>7063935</v>
+        <v>7063889</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291601</v>
+        <v>122291615</v>
       </c>
       <c r="B17" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2378,21 +2343,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2402,10 +2362,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403785</v>
+        <v>403553</v>
       </c>
       <c r="R17" t="n">
-        <v>7064065</v>
+        <v>7063909</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,7 +2402,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,10 +2429,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291615</v>
+        <v>122291610</v>
       </c>
       <c r="B18" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2485,21 +2445,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2509,10 +2464,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403553</v>
+        <v>403537</v>
       </c>
       <c r="R18" t="n">
-        <v>7063909</v>
+        <v>7063905</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2504,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,7 +2531,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291607</v>
+        <v>122291608</v>
       </c>
       <c r="B19" t="n">
         <v>57379</v>
@@ -2594,11 +2549,6 @@
       <c r="E19" t="n">
         <v>100109</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2616,10 +2566,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403575</v>
+        <v>403527</v>
       </c>
       <c r="R19" t="n">
-        <v>7063889</v>
+        <v>7063901</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2683,10 +2633,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291612</v>
+        <v>122291604</v>
       </c>
       <c r="B20" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,21 +2649,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2723,10 +2668,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403831</v>
+        <v>403688</v>
       </c>
       <c r="R20" t="n">
-        <v>7063783</v>
+        <v>7064029</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,7 +2708,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,10 +2735,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291604</v>
+        <v>122291612</v>
       </c>
       <c r="B21" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2806,21 +2751,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,10 +2770,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403688</v>
+        <v>403831</v>
       </c>
       <c r="R21" t="n">
-        <v>7064029</v>
+        <v>7063783</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,7 +2810,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -2225,10 +2225,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291607</v>
+        <v>122291615</v>
       </c>
       <c r="B16" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,16 +2241,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403575</v>
+        <v>403553</v>
       </c>
       <c r="R16" t="n">
-        <v>7063889</v>
+        <v>7063909</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291615</v>
+        <v>122291607</v>
       </c>
       <c r="B17" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,16 +2343,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403553</v>
+        <v>403575</v>
       </c>
       <c r="R17" t="n">
-        <v>7063909</v>
+        <v>7063889</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291601</v>
+        <v>122291609</v>
       </c>
       <c r="B10" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,6 +1631,11 @@
       <c r="E10" t="n">
         <v>100109</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403785</v>
+        <v>403530</v>
       </c>
       <c r="R10" t="n">
-        <v>7064065</v>
+        <v>7063892</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291603</v>
+        <v>122291602</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,6 +1738,11 @@
       <c r="E11" t="n">
         <v>100109</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1750,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403760</v>
+        <v>403779</v>
       </c>
       <c r="R11" t="n">
-        <v>7064050</v>
+        <v>7064045</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291602</v>
+        <v>122291608</v>
       </c>
       <c r="B12" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,6 +1845,11 @@
       <c r="E12" t="n">
         <v>100109</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1852,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403779</v>
+        <v>403527</v>
       </c>
       <c r="R12" t="n">
-        <v>7064045</v>
+        <v>7063901</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1907,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291605</v>
+        <v>122291607</v>
       </c>
       <c r="B13" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,6 +1952,11 @@
       <c r="E13" t="n">
         <v>100109</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1954,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403645</v>
+        <v>403575</v>
       </c>
       <c r="R13" t="n">
-        <v>7063935</v>
+        <v>7063889</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,7 +2044,7 @@
         <v>122291606</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2038,6 +2058,11 @@
       </c>
       <c r="E14" t="n">
         <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2123,10 +2148,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291609</v>
+        <v>122291601</v>
       </c>
       <c r="B15" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2141,6 +2166,11 @@
       <c r="E15" t="n">
         <v>100109</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2158,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403530</v>
+        <v>403785</v>
       </c>
       <c r="R15" t="n">
-        <v>7063892</v>
+        <v>7064065</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2225,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291615</v>
+        <v>122291612</v>
       </c>
       <c r="B16" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2243,6 +2273,11 @@
       <c r="E16" t="n">
         <v>6425</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2260,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403553</v>
+        <v>403831</v>
       </c>
       <c r="R16" t="n">
-        <v>7063909</v>
+        <v>7063783</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291607</v>
+        <v>122291603</v>
       </c>
       <c r="B17" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2345,6 +2380,11 @@
       <c r="E17" t="n">
         <v>100109</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2362,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403575</v>
+        <v>403760</v>
       </c>
       <c r="R17" t="n">
-        <v>7063889</v>
+        <v>7064050</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291610</v>
+        <v>122291615</v>
       </c>
       <c r="B18" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2445,16 +2485,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2464,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403537</v>
+        <v>403553</v>
       </c>
       <c r="R18" t="n">
-        <v>7063905</v>
+        <v>7063909</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,7 +2549,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2531,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291608</v>
+        <v>122291604</v>
       </c>
       <c r="B19" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2549,6 +2594,11 @@
       <c r="E19" t="n">
         <v>100109</v>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2566,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403527</v>
+        <v>403688</v>
       </c>
       <c r="R19" t="n">
-        <v>7063901</v>
+        <v>7064029</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2633,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291604</v>
+        <v>122291610</v>
       </c>
       <c r="B20" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2651,6 +2701,11 @@
       <c r="E20" t="n">
         <v>100109</v>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2668,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403688</v>
+        <v>403537</v>
       </c>
       <c r="R20" t="n">
-        <v>7064029</v>
+        <v>7063905</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,7 +2763,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291612</v>
+        <v>122291605</v>
       </c>
       <c r="B21" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2751,16 +2806,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2770,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403831</v>
+        <v>403645</v>
       </c>
       <c r="R21" t="n">
-        <v>7063783</v>
+        <v>7063935</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,7 +2870,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291609</v>
+        <v>122291612</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403530</v>
+        <v>403831</v>
       </c>
       <c r="R10" t="n">
-        <v>7063892</v>
+        <v>7063783</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,7 +1720,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291602</v>
+        <v>122291607</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403779</v>
+        <v>403575</v>
       </c>
       <c r="R11" t="n">
-        <v>7064045</v>
+        <v>7063889</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291608</v>
+        <v>122291615</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403527</v>
+        <v>403553</v>
       </c>
       <c r="R12" t="n">
-        <v>7063901</v>
+        <v>7063909</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291607</v>
+        <v>122291601</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403575</v>
+        <v>403785</v>
       </c>
       <c r="R13" t="n">
-        <v>7063889</v>
+        <v>7064065</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,7 +2041,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291606</v>
+        <v>122291605</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403596</v>
+        <v>403645</v>
       </c>
       <c r="R14" t="n">
-        <v>7063889</v>
+        <v>7063935</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2148,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291601</v>
+        <v>122291606</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403785</v>
+        <v>403596</v>
       </c>
       <c r="R15" t="n">
-        <v>7064065</v>
+        <v>7063889</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291612</v>
+        <v>122291608</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403831</v>
+        <v>403527</v>
       </c>
       <c r="R16" t="n">
-        <v>7063783</v>
+        <v>7063901</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2469,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291615</v>
+        <v>122291604</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403553</v>
+        <v>403688</v>
       </c>
       <c r="R18" t="n">
-        <v>7063909</v>
+        <v>7064029</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291604</v>
+        <v>122291602</v>
       </c>
       <c r="B19" t="n">
         <v>57383</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403688</v>
+        <v>403779</v>
       </c>
       <c r="R19" t="n">
-        <v>7064029</v>
+        <v>7064045</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,7 +2790,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291605</v>
+        <v>122291609</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403645</v>
+        <v>403530</v>
       </c>
       <c r="R21" t="n">
-        <v>7063935</v>
+        <v>7063892</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1720,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291607</v>
+        <v>122291615</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403575</v>
+        <v>403553</v>
       </c>
       <c r="R11" t="n">
-        <v>7063889</v>
+        <v>7063909</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291615</v>
+        <v>122291607</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403553</v>
+        <v>403575</v>
       </c>
       <c r="R12" t="n">
-        <v>7063909</v>
+        <v>7063889</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291612</v>
+        <v>122291608</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403831</v>
+        <v>403527</v>
       </c>
       <c r="R10" t="n">
-        <v>7063783</v>
+        <v>7063901</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291615</v>
+        <v>122291601</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403553</v>
+        <v>403785</v>
       </c>
       <c r="R11" t="n">
-        <v>7063909</v>
+        <v>7064065</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291607</v>
+        <v>122291602</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403575</v>
+        <v>403779</v>
       </c>
       <c r="R12" t="n">
-        <v>7063889</v>
+        <v>7064045</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291601</v>
+        <v>122291610</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403785</v>
+        <v>403537</v>
       </c>
       <c r="R13" t="n">
-        <v>7064065</v>
+        <v>7063905</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291605</v>
+        <v>122291612</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403645</v>
+        <v>403831</v>
       </c>
       <c r="R14" t="n">
-        <v>7063935</v>
+        <v>7063783</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2148,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291606</v>
+        <v>122291609</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403596</v>
+        <v>403530</v>
       </c>
       <c r="R15" t="n">
-        <v>7063889</v>
+        <v>7063892</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291608</v>
+        <v>122291603</v>
       </c>
       <c r="B16" t="n">
         <v>57383</v>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403527</v>
+        <v>403760</v>
       </c>
       <c r="R16" t="n">
-        <v>7063901</v>
+        <v>7064050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291603</v>
+        <v>122291604</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403760</v>
+        <v>403688</v>
       </c>
       <c r="R17" t="n">
-        <v>7064050</v>
+        <v>7064029</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291604</v>
+        <v>122291607</v>
       </c>
       <c r="B18" t="n">
         <v>57383</v>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403688</v>
+        <v>403575</v>
       </c>
       <c r="R18" t="n">
-        <v>7064029</v>
+        <v>7063889</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291602</v>
+        <v>122291606</v>
       </c>
       <c r="B19" t="n">
         <v>57383</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403779</v>
+        <v>403596</v>
       </c>
       <c r="R19" t="n">
-        <v>7064045</v>
+        <v>7063889</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291610</v>
+        <v>122291615</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403537</v>
+        <v>403553</v>
       </c>
       <c r="R20" t="n">
-        <v>7063905</v>
+        <v>7063909</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,7 +2790,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291609</v>
+        <v>122291605</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403530</v>
+        <v>403645</v>
       </c>
       <c r="R21" t="n">
-        <v>7063892</v>
+        <v>7063935</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,7 +1613,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291608</v>
+        <v>122291610</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403527</v>
+        <v>403537</v>
       </c>
       <c r="R10" t="n">
-        <v>7063901</v>
+        <v>7063905</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291601</v>
+        <v>122291615</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403785</v>
+        <v>403553</v>
       </c>
       <c r="R11" t="n">
-        <v>7064065</v>
+        <v>7063909</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291602</v>
+        <v>122291607</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403779</v>
+        <v>403575</v>
       </c>
       <c r="R12" t="n">
-        <v>7064045</v>
+        <v>7063889</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291610</v>
+        <v>122291602</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403537</v>
+        <v>403779</v>
       </c>
       <c r="R13" t="n">
-        <v>7063905</v>
+        <v>7064045</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291612</v>
+        <v>122291609</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403831</v>
+        <v>403530</v>
       </c>
       <c r="R14" t="n">
-        <v>7063783</v>
+        <v>7063892</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2148,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291609</v>
+        <v>122291606</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403530</v>
+        <v>403596</v>
       </c>
       <c r="R15" t="n">
-        <v>7063892</v>
+        <v>7063889</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291603</v>
+        <v>122291601</v>
       </c>
       <c r="B16" t="n">
         <v>57383</v>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403760</v>
+        <v>403785</v>
       </c>
       <c r="R16" t="n">
-        <v>7064050</v>
+        <v>7064065</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291604</v>
+        <v>122291605</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403688</v>
+        <v>403645</v>
       </c>
       <c r="R17" t="n">
-        <v>7064029</v>
+        <v>7063935</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291607</v>
+        <v>122291603</v>
       </c>
       <c r="B18" t="n">
         <v>57383</v>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403575</v>
+        <v>403760</v>
       </c>
       <c r="R18" t="n">
-        <v>7063889</v>
+        <v>7064050</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291606</v>
+        <v>122291604</v>
       </c>
       <c r="B19" t="n">
         <v>57383</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403596</v>
+        <v>403688</v>
       </c>
       <c r="R19" t="n">
-        <v>7063889</v>
+        <v>7064029</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,7 +2683,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291615</v>
+        <v>122291612</v>
       </c>
       <c r="B20" t="n">
         <v>78656</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403553</v>
+        <v>403831</v>
       </c>
       <c r="R20" t="n">
-        <v>7063909</v>
+        <v>7063783</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291605</v>
+        <v>122291608</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403645</v>
+        <v>403527</v>
       </c>
       <c r="R21" t="n">
-        <v>7063935</v>
+        <v>7063901</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,7 +1613,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291610</v>
+        <v>122291603</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403537</v>
+        <v>403760</v>
       </c>
       <c r="R10" t="n">
-        <v>7063905</v>
+        <v>7064050</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291615</v>
+        <v>122291601</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403553</v>
+        <v>403785</v>
       </c>
       <c r="R11" t="n">
-        <v>7063909</v>
+        <v>7064065</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291607</v>
+        <v>122291610</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403575</v>
+        <v>403537</v>
       </c>
       <c r="R12" t="n">
-        <v>7063889</v>
+        <v>7063905</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291602</v>
+        <v>122291606</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403779</v>
+        <v>403596</v>
       </c>
       <c r="R13" t="n">
-        <v>7064045</v>
+        <v>7063889</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291609</v>
+        <v>122291605</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403530</v>
+        <v>403645</v>
       </c>
       <c r="R14" t="n">
-        <v>7063892</v>
+        <v>7063935</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2148,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291606</v>
+        <v>122291602</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403596</v>
+        <v>403779</v>
       </c>
       <c r="R15" t="n">
-        <v>7063889</v>
+        <v>7064045</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291601</v>
+        <v>122291609</v>
       </c>
       <c r="B16" t="n">
         <v>57383</v>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403785</v>
+        <v>403530</v>
       </c>
       <c r="R16" t="n">
-        <v>7064065</v>
+        <v>7063892</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291605</v>
+        <v>122291604</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403645</v>
+        <v>403688</v>
       </c>
       <c r="R17" t="n">
-        <v>7063935</v>
+        <v>7064029</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291603</v>
+        <v>122291607</v>
       </c>
       <c r="B18" t="n">
         <v>57383</v>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403760</v>
+        <v>403575</v>
       </c>
       <c r="R18" t="n">
-        <v>7064050</v>
+        <v>7063889</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291604</v>
+        <v>122291612</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403688</v>
+        <v>403831</v>
       </c>
       <c r="R19" t="n">
-        <v>7064029</v>
+        <v>7063783</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291612</v>
+        <v>122291608</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403831</v>
+        <v>403527</v>
       </c>
       <c r="R20" t="n">
-        <v>7063783</v>
+        <v>7063901</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291608</v>
+        <v>122291615</v>
       </c>
       <c r="B21" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403527</v>
+        <v>403553</v>
       </c>
       <c r="R21" t="n">
-        <v>7063901</v>
+        <v>7063909</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291603</v>
+        <v>122291604</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403760</v>
+        <v>403688</v>
       </c>
       <c r="R10" t="n">
-        <v>7064050</v>
+        <v>7064029</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291601</v>
+        <v>122291603</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403785</v>
+        <v>403760</v>
       </c>
       <c r="R11" t="n">
-        <v>7064065</v>
+        <v>7064050</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291610</v>
+        <v>122291606</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403537</v>
+        <v>403596</v>
       </c>
       <c r="R12" t="n">
-        <v>7063905</v>
+        <v>7063889</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291606</v>
+        <v>122291612</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403596</v>
+        <v>403831</v>
       </c>
       <c r="R13" t="n">
-        <v>7063889</v>
+        <v>7063783</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291605</v>
+        <v>122291608</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403645</v>
+        <v>403527</v>
       </c>
       <c r="R14" t="n">
-        <v>7063935</v>
+        <v>7063901</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,7 +2151,7 @@
         <v>122291602</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291609</v>
+        <v>122291601</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403530</v>
+        <v>403785</v>
       </c>
       <c r="R16" t="n">
-        <v>7063892</v>
+        <v>7064065</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291604</v>
+        <v>122291609</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403688</v>
+        <v>403530</v>
       </c>
       <c r="R17" t="n">
-        <v>7064029</v>
+        <v>7063892</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,7 +2472,7 @@
         <v>122291607</v>
       </c>
       <c r="B18" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291612</v>
+        <v>122291615</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403831</v>
+        <v>403553</v>
       </c>
       <c r="R19" t="n">
-        <v>7063783</v>
+        <v>7063909</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291608</v>
+        <v>122291610</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403527</v>
+        <v>403537</v>
       </c>
       <c r="R20" t="n">
-        <v>7063901</v>
+        <v>7063905</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291615</v>
+        <v>122291605</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403553</v>
+        <v>403645</v>
       </c>
       <c r="R21" t="n">
-        <v>7063909</v>
+        <v>7063935</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,7 +1613,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291604</v>
+        <v>122291609</v>
       </c>
       <c r="B10" t="n">
         <v>57384</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403688</v>
+        <v>403530</v>
       </c>
       <c r="R10" t="n">
-        <v>7064029</v>
+        <v>7063892</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,7 +1720,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291603</v>
+        <v>122291606</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403760</v>
+        <v>403596</v>
       </c>
       <c r="R11" t="n">
-        <v>7064050</v>
+        <v>7063889</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291606</v>
+        <v>122291610</v>
       </c>
       <c r="B12" t="n">
         <v>57384</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403596</v>
+        <v>403537</v>
       </c>
       <c r="R12" t="n">
-        <v>7063889</v>
+        <v>7063905</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291612</v>
+        <v>122291607</v>
       </c>
       <c r="B13" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403831</v>
+        <v>403575</v>
       </c>
       <c r="R13" t="n">
-        <v>7063783</v>
+        <v>7063889</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,7 +2041,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291608</v>
+        <v>122291602</v>
       </c>
       <c r="B14" t="n">
         <v>57384</v>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403527</v>
+        <v>403779</v>
       </c>
       <c r="R14" t="n">
-        <v>7063901</v>
+        <v>7064045</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2148,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291602</v>
+        <v>122291608</v>
       </c>
       <c r="B15" t="n">
         <v>57384</v>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403779</v>
+        <v>403527</v>
       </c>
       <c r="R15" t="n">
-        <v>7064045</v>
+        <v>7063901</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2255,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291601</v>
+        <v>122291605</v>
       </c>
       <c r="B16" t="n">
         <v>57384</v>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403785</v>
+        <v>403645</v>
       </c>
       <c r="R16" t="n">
-        <v>7064065</v>
+        <v>7063935</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291609</v>
+        <v>122291601</v>
       </c>
       <c r="B17" t="n">
         <v>57384</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403530</v>
+        <v>403785</v>
       </c>
       <c r="R17" t="n">
-        <v>7063892</v>
+        <v>7064065</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291607</v>
+        <v>122291615</v>
       </c>
       <c r="B18" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403575</v>
+        <v>403553</v>
       </c>
       <c r="R18" t="n">
-        <v>7063889</v>
+        <v>7063909</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291615</v>
+        <v>122291603</v>
       </c>
       <c r="B19" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403553</v>
+        <v>403760</v>
       </c>
       <c r="R19" t="n">
-        <v>7063909</v>
+        <v>7064050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291610</v>
+        <v>122291612</v>
       </c>
       <c r="B20" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403537</v>
+        <v>403831</v>
       </c>
       <c r="R20" t="n">
-        <v>7063905</v>
+        <v>7063783</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,7 +2790,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291605</v>
+        <v>122291604</v>
       </c>
       <c r="B21" t="n">
         <v>57384</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403645</v>
+        <v>403688</v>
       </c>
       <c r="R21" t="n">
-        <v>7063935</v>
+        <v>7064029</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5987-2021 artfynd.xlsx
+++ b/artfynd/A 5987-2021 artfynd.xlsx
@@ -1613,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291609</v>
+        <v>122291615</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403530</v>
+        <v>403553</v>
       </c>
       <c r="R10" t="n">
-        <v>7063892</v>
+        <v>7063909</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,7 +1720,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291606</v>
+        <v>122291608</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403596</v>
+        <v>403527</v>
       </c>
       <c r="R11" t="n">
-        <v>7063889</v>
+        <v>7063901</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291610</v>
+        <v>122291601</v>
       </c>
       <c r="B12" t="n">
         <v>57384</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403537</v>
+        <v>403785</v>
       </c>
       <c r="R12" t="n">
-        <v>7063905</v>
+        <v>7064065</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291607</v>
+        <v>122291604</v>
       </c>
       <c r="B13" t="n">
         <v>57384</v>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403575</v>
+        <v>403688</v>
       </c>
       <c r="R13" t="n">
-        <v>7063889</v>
+        <v>7064029</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291602</v>
+        <v>122291603</v>
       </c>
       <c r="B14" t="n">
         <v>57384</v>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403779</v>
+        <v>403760</v>
       </c>
       <c r="R14" t="n">
-        <v>7064045</v>
+        <v>7064050</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2148,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291608</v>
+        <v>122291609</v>
       </c>
       <c r="B15" t="n">
         <v>57384</v>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403527</v>
+        <v>403530</v>
       </c>
       <c r="R15" t="n">
-        <v>7063901</v>
+        <v>7063892</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2362,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291601</v>
+        <v>122291612</v>
       </c>
       <c r="B17" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2378,21 +2378,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403785</v>
+        <v>403831</v>
       </c>
       <c r="R17" t="n">
-        <v>7064065</v>
+        <v>7063783</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291615</v>
+        <v>122291610</v>
       </c>
       <c r="B18" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403553</v>
+        <v>403537</v>
       </c>
       <c r="R18" t="n">
-        <v>7063909</v>
+        <v>7063905</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291603</v>
+        <v>122291602</v>
       </c>
       <c r="B19" t="n">
         <v>57384</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403760</v>
+        <v>403779</v>
       </c>
       <c r="R19" t="n">
-        <v>7064050</v>
+        <v>7064045</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291612</v>
+        <v>122291607</v>
       </c>
       <c r="B20" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403831</v>
+        <v>403575</v>
       </c>
       <c r="R20" t="n">
-        <v>7063783</v>
+        <v>7063889</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,7 +2790,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291604</v>
+        <v>122291606</v>
       </c>
       <c r="B21" t="n">
         <v>57384</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403688</v>
+        <v>403596</v>
       </c>
       <c r="R21" t="n">
-        <v>7064029</v>
+        <v>7063889</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
